--- a/daftar akun.xlsx
+++ b/daftar akun.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/azkalfikri/Projects/portalrb/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6A05014-A108-2C45-91EE-BF6CABB04996}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEDC2D43-E746-B24B-9F3A-58524DF5FA34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
